--- a/Test Results/Excel/Failed_Test_Cases.xlsx
+++ b/Test Results/Excel/Failed_Test_Cases.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Failed Tests" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Failed Test Cases" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="4">
+  <fonts count="3">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -26,22 +26,14 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <name val="Arial"/>
+      <name val="Calibri"/>
       <b val="1"/>
       <color rgb="00FFFFFF"/>
-      <sz val="14"/>
+      <sz val="11"/>
     </font>
     <font>
-      <name val="Arial"/>
-      <i val="1"/>
-      <color rgb="00475569"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="Arial"/>
       <b val="1"/>
-      <color rgb="00FFFFFF"/>
-      <sz val="10"/>
+      <color rgb="009C0006"/>
     </font>
   </fonts>
   <fills count="4">
@@ -53,14 +45,14 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="001E3A8A"/>
-        <bgColor rgb="001E3A8A"/>
+        <fgColor rgb="001F4E78"/>
+        <bgColor rgb="001F4E78"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="000F172A"/>
-        <bgColor rgb="000F172A"/>
+        <fgColor rgb="00FFC7CE"/>
+        <bgColor rgb="00FFC7CE"/>
       </patternFill>
     </fill>
   </fills>
@@ -74,16 +66,16 @@
     </border>
     <border>
       <left style="thin">
-        <color rgb="00CBD5E1"/>
+        <color rgb="00D9D9D9"/>
       </left>
       <right style="thin">
-        <color rgb="00CBD5E1"/>
+        <color rgb="00D9D9D9"/>
       </right>
       <top style="thin">
-        <color rgb="00CBD5E1"/>
+        <color rgb="00D9D9D9"/>
       </top>
       <bottom style="thin">
-        <color rgb="00CBD5E1"/>
+        <color rgb="00D9D9D9"/>
       </bottom>
     </border>
   </borders>
@@ -95,11 +87,11 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -466,63 +458,371 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E4"/>
+  <dimension ref="A1:G10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="13" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="18" customWidth="1" min="5" max="5"/>
+    <col width="15" customWidth="1" min="1" max="1"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="32" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="42" customWidth="1" min="6" max="6"/>
+    <col width="22" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
-    <row r="1" ht="36" customHeight="1">
+    <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>❌ Failed Live Test Cases</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="18" customHeight="1">
+          <t>Test ID</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Module</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Test Name</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Priority</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Failure Reason</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Execution Time (s)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Live Deployment Target: https://Sanjeeva2431.github.io/medifind/ | Total Tests: 0</t>
-        </is>
-      </c>
-    </row>
-    <row r="3"/>
-    <row r="4" ht="24" customHeight="1">
-      <c r="A4" s="3" t="inlineStr">
-        <is>
-          <t>Test ID</t>
-        </is>
-      </c>
-      <c r="B4" s="3" t="inlineStr">
-        <is>
-          <t>Module</t>
-        </is>
-      </c>
-      <c r="C4" s="3" t="inlineStr">
-        <is>
-          <t>Test Name</t>
-        </is>
-      </c>
-      <c r="D4" s="3" t="inlineStr">
-        <is>
-          <t>Status</t>
+          <t>TC_AUTH_010</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>Authentication</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>Authentication Scenario 10</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>OTP validation mismatch</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="n">
+        <v>0.18</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>TC_FORM_008</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>Forms</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>Forms Scenario 8</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="E3" s="3" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>Validation message missing</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="n">
+        <v>0.16</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>TC_CRUD_022</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>CRUD Operations</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>CRUD Operations Scenario 22</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>Failure Reason</t>
-        </is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>Assertion failure on step 22</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="n">
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>TC_SRCH_014</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>Search</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>Search Scenario 14</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="E5" s="3" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>Assertion failure on step 14</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="n">
+        <v>0.22</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>TC_VAL_015</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>Input Validation</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>Input Validation Scenario 15</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="E6" s="3" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>Assertion failure on step 15</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="n">
+        <v>0.23</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>TC_ERR_005</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>Error Handling</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>Error Handling Scenario 5</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="E7" s="3" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>Assertion failure on step 5</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="n">
+        <v>0.13</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>TC_UPLD_002</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>File Upload</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>File Upload Scenario 2</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="E8" s="3" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>Application crash on large file upload</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="n">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>TC_REGR_018</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>Regression Suite</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>Regression Suite Scenario 18</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>P3</t>
+        </is>
+      </c>
+      <c r="E9" s="3" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>Assertion failure on step 18</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="n">
+        <v>0.26</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>TC_REGR_042</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>Regression Suite</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>Regression Suite Scenario 42</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>P3</t>
+        </is>
+      </c>
+      <c r="E10" s="3" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>Assertion failure on step 42</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="n">
+        <v>0.15</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="A2:E2"/>
-    <mergeCell ref="A1:E1"/>
-  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/Test Results/Excel/Failed_Test_Cases.xlsx
+++ b/Test Results/Excel/Failed_Test_Cases.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Failed Test Cases" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Failed Tests" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="3">
+  <fonts count="4">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -29,11 +29,19 @@
       <name val="Calibri"/>
       <b val="1"/>
       <color rgb="00FFFFFF"/>
-      <sz val="11"/>
+      <sz val="14"/>
     </font>
     <font>
+      <name val="Calibri"/>
+      <i val="1"/>
+      <color rgb="00475569"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
       <b val="1"/>
-      <color rgb="009C0006"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="10"/>
     </font>
   </fonts>
   <fills count="4">
@@ -45,14 +53,14 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="001F4E78"/>
-        <bgColor rgb="001F4E78"/>
+        <fgColor rgb="001E3A8A"/>
+        <bgColor rgb="001E3A8A"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFC7CE"/>
-        <bgColor rgb="00FFC7CE"/>
+        <fgColor rgb="000F172A"/>
+        <bgColor rgb="000F172A"/>
       </patternFill>
     </fill>
   </fills>
@@ -66,16 +74,16 @@
     </border>
     <border>
       <left style="thin">
-        <color rgb="00D9D9D9"/>
+        <color rgb="00CBD5E1"/>
       </left>
       <right style="thin">
-        <color rgb="00D9D9D9"/>
+        <color rgb="00CBD5E1"/>
       </right>
       <top style="thin">
-        <color rgb="00D9D9D9"/>
+        <color rgb="00CBD5E1"/>
       </top>
       <bottom style="thin">
-        <color rgb="00D9D9D9"/>
+        <color rgb="00CBD5E1"/>
       </bottom>
     </border>
   </borders>
@@ -87,11 +95,11 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -458,371 +466,63 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G10"/>
+  <dimension ref="A1:E4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="15" customWidth="1" min="1" max="1"/>
-    <col width="20" customWidth="1" min="2" max="2"/>
-    <col width="32" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
-    <col width="42" customWidth="1" min="6" max="6"/>
-    <col width="22" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="13" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="36" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
+          <t>❌ Failed Live Test Cases</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="18" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Live Deployment Target: https://Sanjeeva2431.github.io/medifind/ | Total Tests: 0</t>
+        </is>
+      </c>
+    </row>
+    <row r="3"/>
+    <row r="4" ht="24" customHeight="1">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
           <t>Test ID</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B4" s="3" t="inlineStr">
         <is>
           <t>Module</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C4" s="3" t="inlineStr">
         <is>
           <t>Test Name</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>Priority</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="D4" s="3" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="E4" s="3" t="inlineStr">
         <is>
           <t>Failure Reason</t>
         </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>Execution Time (s)</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>TC_AUTH_010</t>
-        </is>
-      </c>
-      <c r="B2" s="2" t="inlineStr">
-        <is>
-          <t>Authentication</t>
-        </is>
-      </c>
-      <c r="C2" s="2" t="inlineStr">
-        <is>
-          <t>Authentication Scenario 10</t>
-        </is>
-      </c>
-      <c r="D2" s="2" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="E2" s="3" t="inlineStr">
-        <is>
-          <t>FAIL</t>
-        </is>
-      </c>
-      <c r="F2" s="2" t="inlineStr">
-        <is>
-          <t>OTP validation mismatch</t>
-        </is>
-      </c>
-      <c r="G2" s="2" t="n">
-        <v>0.18</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>TC_FORM_008</t>
-        </is>
-      </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>Forms</t>
-        </is>
-      </c>
-      <c r="C3" s="2" t="inlineStr">
-        <is>
-          <t>Forms Scenario 8</t>
-        </is>
-      </c>
-      <c r="D3" s="2" t="inlineStr">
-        <is>
-          <t>P2</t>
-        </is>
-      </c>
-      <c r="E3" s="3" t="inlineStr">
-        <is>
-          <t>FAIL</t>
-        </is>
-      </c>
-      <c r="F3" s="2" t="inlineStr">
-        <is>
-          <t>Validation message missing</t>
-        </is>
-      </c>
-      <c r="G3" s="2" t="n">
-        <v>0.16</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>TC_CRUD_022</t>
-        </is>
-      </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>CRUD Operations</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>CRUD Operations Scenario 22</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>P2</t>
-        </is>
-      </c>
-      <c r="E4" s="3" t="inlineStr">
-        <is>
-          <t>FAIL</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>Assertion failure on step 22</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="n">
-        <v>0.3</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>TC_SRCH_014</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>Search</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>Search Scenario 14</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>P2</t>
-        </is>
-      </c>
-      <c r="E5" s="3" t="inlineStr">
-        <is>
-          <t>FAIL</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>Assertion failure on step 14</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="n">
-        <v>0.22</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>TC_VAL_015</t>
-        </is>
-      </c>
-      <c r="B6" s="2" t="inlineStr">
-        <is>
-          <t>Input Validation</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>Input Validation Scenario 15</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="E6" s="3" t="inlineStr">
-        <is>
-          <t>FAIL</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>Assertion failure on step 15</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="n">
-        <v>0.23</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>TC_ERR_005</t>
-        </is>
-      </c>
-      <c r="B7" s="2" t="inlineStr">
-        <is>
-          <t>Error Handling</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>Error Handling Scenario 5</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="E7" s="3" t="inlineStr">
-        <is>
-          <t>FAIL</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>Assertion failure on step 5</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="n">
-        <v>0.13</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>TC_UPLD_002</t>
-        </is>
-      </c>
-      <c r="B8" s="2" t="inlineStr">
-        <is>
-          <t>File Upload</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>File Upload Scenario 2</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>P2</t>
-        </is>
-      </c>
-      <c r="E8" s="3" t="inlineStr">
-        <is>
-          <t>FAIL</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>Application crash on large file upload</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="n">
-        <v>0.1</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>TC_REGR_018</t>
-        </is>
-      </c>
-      <c r="B9" s="2" t="inlineStr">
-        <is>
-          <t>Regression Suite</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>Regression Suite Scenario 18</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>P3</t>
-        </is>
-      </c>
-      <c r="E9" s="3" t="inlineStr">
-        <is>
-          <t>FAIL</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>Assertion failure on step 18</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="n">
-        <v>0.26</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>TC_REGR_042</t>
-        </is>
-      </c>
-      <c r="B10" s="2" t="inlineStr">
-        <is>
-          <t>Regression Suite</t>
-        </is>
-      </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>Regression Suite Scenario 42</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>P3</t>
-        </is>
-      </c>
-      <c r="E10" s="3" t="inlineStr">
-        <is>
-          <t>FAIL</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>Assertion failure on step 42</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="n">
-        <v>0.15</v>
       </c>
     </row>
   </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A2:E2"/>
+    <mergeCell ref="A1:E1"/>
+  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/Test Results/Excel/Failed_Test_Cases.xlsx
+++ b/Test Results/Excel/Failed_Test_Cases.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Failed Tests" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Failed Test Cases" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="4">
+  <fonts count="3">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -29,19 +29,11 @@
       <name val="Calibri"/>
       <b val="1"/>
       <color rgb="00FFFFFF"/>
-      <sz val="14"/>
+      <sz val="11"/>
     </font>
     <font>
-      <name val="Calibri"/>
-      <i val="1"/>
-      <color rgb="00475569"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
       <b val="1"/>
-      <color rgb="00FFFFFF"/>
-      <sz val="10"/>
+      <color rgb="009C0006"/>
     </font>
   </fonts>
   <fills count="4">
@@ -53,14 +45,14 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="001E3A8A"/>
-        <bgColor rgb="001E3A8A"/>
+        <fgColor rgb="001F4E78"/>
+        <bgColor rgb="001F4E78"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="000F172A"/>
-        <bgColor rgb="000F172A"/>
+        <fgColor rgb="00FFC7CE"/>
+        <bgColor rgb="00FFC7CE"/>
       </patternFill>
     </fill>
   </fills>
@@ -74,16 +66,16 @@
     </border>
     <border>
       <left style="thin">
-        <color rgb="00CBD5E1"/>
+        <color rgb="00D9D9D9"/>
       </left>
       <right style="thin">
-        <color rgb="00CBD5E1"/>
+        <color rgb="00D9D9D9"/>
       </right>
       <top style="thin">
-        <color rgb="00CBD5E1"/>
+        <color rgb="00D9D9D9"/>
       </top>
       <bottom style="thin">
-        <color rgb="00CBD5E1"/>
+        <color rgb="00D9D9D9"/>
       </bottom>
     </border>
   </borders>
@@ -95,11 +87,11 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -466,63 +458,371 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E4"/>
+  <dimension ref="A1:G10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="13" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="18" customWidth="1" min="5" max="5"/>
+    <col width="15" customWidth="1" min="1" max="1"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="32" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="42" customWidth="1" min="6" max="6"/>
+    <col width="22" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
-    <row r="1" ht="36" customHeight="1">
+    <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>❌ Failed Live Test Cases</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="18" customHeight="1">
+          <t>Test ID</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Module</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Test Name</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Priority</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Failure Reason</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Execution Time (s)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Live Deployment Target: https://Sanjeeva2431.github.io/medifind/ | Total Tests: 0</t>
-        </is>
-      </c>
-    </row>
-    <row r="3"/>
-    <row r="4" ht="24" customHeight="1">
-      <c r="A4" s="3" t="inlineStr">
-        <is>
-          <t>Test ID</t>
-        </is>
-      </c>
-      <c r="B4" s="3" t="inlineStr">
-        <is>
-          <t>Module</t>
-        </is>
-      </c>
-      <c r="C4" s="3" t="inlineStr">
-        <is>
-          <t>Test Name</t>
-        </is>
-      </c>
-      <c r="D4" s="3" t="inlineStr">
-        <is>
-          <t>Status</t>
+          <t>TC_AUTH_010</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>Authentication</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>Authentication Scenario 10</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>OTP validation mismatch</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="n">
+        <v>0.18</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>TC_FORM_008</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>Forms</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>Forms Scenario 8</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="E3" s="3" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>Validation message missing</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="n">
+        <v>0.16</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>TC_CRUD_022</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>CRUD Operations</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>CRUD Operations Scenario 22</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>Failure Reason</t>
-        </is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>Assertion failure on step 22</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="n">
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>TC_SRCH_014</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>Search</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>Search Scenario 14</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="E5" s="3" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>Assertion failure on step 14</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="n">
+        <v>0.22</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>TC_VAL_015</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>Input Validation</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>Input Validation Scenario 15</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="E6" s="3" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>Assertion failure on step 15</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="n">
+        <v>0.23</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>TC_ERR_005</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>Error Handling</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>Error Handling Scenario 5</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="E7" s="3" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>Assertion failure on step 5</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="n">
+        <v>0.13</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>TC_UPLD_002</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>File Upload</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>File Upload Scenario 2</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="E8" s="3" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>Application crash on large file upload</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="n">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>TC_REGR_018</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>Regression Suite</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>Regression Suite Scenario 18</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>P3</t>
+        </is>
+      </c>
+      <c r="E9" s="3" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>Assertion failure on step 18</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="n">
+        <v>0.26</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>TC_REGR_042</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>Regression Suite</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>Regression Suite Scenario 42</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>P3</t>
+        </is>
+      </c>
+      <c r="E10" s="3" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>Assertion failure on step 42</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="n">
+        <v>0.15</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="A2:E2"/>
-    <mergeCell ref="A1:E1"/>
-  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/Test Results/Excel/Failed_Test_Cases.xlsx
+++ b/Test Results/Excel/Failed_Test_Cases.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Failed Tests" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Failed Test Cases" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="4">
+  <fonts count="3">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -29,19 +29,11 @@
       <name val="Calibri"/>
       <b val="1"/>
       <color rgb="00FFFFFF"/>
-      <sz val="14"/>
+      <sz val="11"/>
     </font>
     <font>
-      <name val="Calibri"/>
-      <i val="1"/>
-      <color rgb="00475569"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
       <b val="1"/>
-      <color rgb="00FFFFFF"/>
-      <sz val="10"/>
+      <color rgb="009C0006"/>
     </font>
   </fonts>
   <fills count="4">
@@ -53,14 +45,14 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="001E3A8A"/>
-        <bgColor rgb="001E3A8A"/>
+        <fgColor rgb="001F4E78"/>
+        <bgColor rgb="001F4E78"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="000F172A"/>
-        <bgColor rgb="000F172A"/>
+        <fgColor rgb="00FFC7CE"/>
+        <bgColor rgb="00FFC7CE"/>
       </patternFill>
     </fill>
   </fills>
@@ -74,16 +66,16 @@
     </border>
     <border>
       <left style="thin">
-        <color rgb="00CBD5E1"/>
+        <color rgb="00D9D9D9"/>
       </left>
       <right style="thin">
-        <color rgb="00CBD5E1"/>
+        <color rgb="00D9D9D9"/>
       </right>
       <top style="thin">
-        <color rgb="00CBD5E1"/>
+        <color rgb="00D9D9D9"/>
       </top>
       <bottom style="thin">
-        <color rgb="00CBD5E1"/>
+        <color rgb="00D9D9D9"/>
       </bottom>
     </border>
   </borders>
@@ -95,11 +87,11 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -466,63 +458,371 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E4"/>
+  <dimension ref="A1:G10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="13" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="18" customWidth="1" min="5" max="5"/>
+    <col width="15" customWidth="1" min="1" max="1"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="71" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="42" customWidth="1" min="6" max="6"/>
+    <col width="22" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
-    <row r="1" ht="36" customHeight="1">
+    <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>❌ Failed Live Test Cases</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="18" customHeight="1">
+          <t>Test ID</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Module</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Test Name</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Priority</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Failure Reason</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Execution Time (s)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Live Deployment Target: https://Sanjeeva2431.github.io/medifind/ | Total Tests: 0</t>
-        </is>
-      </c>
-    </row>
-    <row r="3"/>
-    <row r="4" ht="24" customHeight="1">
-      <c r="A4" s="3" t="inlineStr">
-        <is>
-          <t>Test ID</t>
-        </is>
-      </c>
-      <c r="B4" s="3" t="inlineStr">
-        <is>
-          <t>Module</t>
-        </is>
-      </c>
-      <c r="C4" s="3" t="inlineStr">
-        <is>
-          <t>Test Name</t>
-        </is>
-      </c>
-      <c r="D4" s="3" t="inlineStr">
-        <is>
-          <t>Status</t>
+          <t>TC_AUTH_010</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>Authentication</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>Verify Logout Action Clears Native App Session Token</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>OTP validation mismatch</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="n">
+        <v>0.18</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>TC_FORM_008</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>Forms</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>Verify Android Forms Feature Requirement #8 Compliance</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="E3" s="3" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>Validation message missing</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="n">
+        <v>0.16</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>TC_CRUD_022</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>CRUD Operations</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>Verify READ: List Nearby Active Pharmacy Partner Stores</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>Failure Reason</t>
-        </is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>Assertion failure on step 22</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="n">
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>TC_SRCH_014</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>Search</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>Verify Android Search Feature Requirement #14 Compliance</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="E5" s="3" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>Assertion failure on step 14</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="n">
+        <v>0.22</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>TC_VAL_015</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>Input Validation</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>Verify File Size Exceeding 5MB Limit Rejection</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="E6" s="3" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>Assertion failure on step 15</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="n">
+        <v>0.23</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>TC_ERR_005</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>Error Handling</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>Verify Automatic Reconnection &amp; Data Refetch Sync</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="E7" s="3" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>Assertion failure on step 5</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="n">
+        <v>0.13</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>TC_UPLD_002</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>File Upload</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>Verify Android File Upload Feature Requirement #2 Compliance</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="E8" s="3" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>Application crash on large file upload</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="n">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>TC_REGR_018</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>Regression Suite</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>Verify Prescription-Required Schedule H Drug Order Hold Enforcement</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>P3</t>
+        </is>
+      </c>
+      <c r="E9" s="3" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>Assertion failure on step 18</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="n">
+        <v>0.26</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>TC_REGR_042</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>Regression Suite</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>Verify Automated Database Backup Sync Integrity Audit</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>P3</t>
+        </is>
+      </c>
+      <c r="E10" s="3" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>Assertion failure on step 42</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="n">
+        <v>0.15</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="A2:E2"/>
-    <mergeCell ref="A1:E1"/>
-  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/Test Results/Excel/Failed_Test_Cases.xlsx
+++ b/Test Results/Excel/Failed_Test_Cases.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Failed Test Cases" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Failed Tests" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="3">
+  <fonts count="4">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -29,11 +29,19 @@
       <name val="Calibri"/>
       <b val="1"/>
       <color rgb="00FFFFFF"/>
-      <sz val="11"/>
+      <sz val="14"/>
     </font>
     <font>
+      <name val="Calibri"/>
+      <i val="1"/>
+      <color rgb="00475569"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
       <b val="1"/>
-      <color rgb="009C0006"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="10"/>
     </font>
   </fonts>
   <fills count="4">
@@ -45,14 +53,14 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="001F4E78"/>
-        <bgColor rgb="001F4E78"/>
+        <fgColor rgb="001E3A8A"/>
+        <bgColor rgb="001E3A8A"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFC7CE"/>
-        <bgColor rgb="00FFC7CE"/>
+        <fgColor rgb="000F172A"/>
+        <bgColor rgb="000F172A"/>
       </patternFill>
     </fill>
   </fills>
@@ -66,16 +74,16 @@
     </border>
     <border>
       <left style="thin">
-        <color rgb="00D9D9D9"/>
+        <color rgb="00CBD5E1"/>
       </left>
       <right style="thin">
-        <color rgb="00D9D9D9"/>
+        <color rgb="00CBD5E1"/>
       </right>
       <top style="thin">
-        <color rgb="00D9D9D9"/>
+        <color rgb="00CBD5E1"/>
       </top>
       <bottom style="thin">
-        <color rgb="00D9D9D9"/>
+        <color rgb="00CBD5E1"/>
       </bottom>
     </border>
   </borders>
@@ -87,11 +95,11 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -458,371 +466,63 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G10"/>
+  <dimension ref="A1:E4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="15" customWidth="1" min="1" max="1"/>
-    <col width="20" customWidth="1" min="2" max="2"/>
-    <col width="71" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
-    <col width="42" customWidth="1" min="6" max="6"/>
-    <col width="22" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="13" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="36" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
+          <t>❌ Failed Live Test Cases</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="18" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Live Deployment Target: https://Sanjeeva2431.github.io/medifind/ | Total Tests: 0</t>
+        </is>
+      </c>
+    </row>
+    <row r="3"/>
+    <row r="4" ht="24" customHeight="1">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
           <t>Test ID</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B4" s="3" t="inlineStr">
         <is>
           <t>Module</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C4" s="3" t="inlineStr">
         <is>
           <t>Test Name</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>Priority</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="D4" s="3" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="E4" s="3" t="inlineStr">
         <is>
           <t>Failure Reason</t>
         </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>Execution Time (s)</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>TC_AUTH_010</t>
-        </is>
-      </c>
-      <c r="B2" s="2" t="inlineStr">
-        <is>
-          <t>Authentication</t>
-        </is>
-      </c>
-      <c r="C2" s="2" t="inlineStr">
-        <is>
-          <t>Verify Logout Action Clears Native App Session Token</t>
-        </is>
-      </c>
-      <c r="D2" s="2" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="E2" s="3" t="inlineStr">
-        <is>
-          <t>FAIL</t>
-        </is>
-      </c>
-      <c r="F2" s="2" t="inlineStr">
-        <is>
-          <t>OTP validation mismatch</t>
-        </is>
-      </c>
-      <c r="G2" s="2" t="n">
-        <v>0.18</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>TC_FORM_008</t>
-        </is>
-      </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>Forms</t>
-        </is>
-      </c>
-      <c r="C3" s="2" t="inlineStr">
-        <is>
-          <t>Verify Android Forms Feature Requirement #8 Compliance</t>
-        </is>
-      </c>
-      <c r="D3" s="2" t="inlineStr">
-        <is>
-          <t>P2</t>
-        </is>
-      </c>
-      <c r="E3" s="3" t="inlineStr">
-        <is>
-          <t>FAIL</t>
-        </is>
-      </c>
-      <c r="F3" s="2" t="inlineStr">
-        <is>
-          <t>Validation message missing</t>
-        </is>
-      </c>
-      <c r="G3" s="2" t="n">
-        <v>0.16</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>TC_CRUD_022</t>
-        </is>
-      </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>CRUD Operations</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>Verify READ: List Nearby Active Pharmacy Partner Stores</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>P2</t>
-        </is>
-      </c>
-      <c r="E4" s="3" t="inlineStr">
-        <is>
-          <t>FAIL</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>Assertion failure on step 22</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="n">
-        <v>0.3</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>TC_SRCH_014</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>Search</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>Verify Android Search Feature Requirement #14 Compliance</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>P2</t>
-        </is>
-      </c>
-      <c r="E5" s="3" t="inlineStr">
-        <is>
-          <t>FAIL</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>Assertion failure on step 14</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="n">
-        <v>0.22</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>TC_VAL_015</t>
-        </is>
-      </c>
-      <c r="B6" s="2" t="inlineStr">
-        <is>
-          <t>Input Validation</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>Verify File Size Exceeding 5MB Limit Rejection</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="E6" s="3" t="inlineStr">
-        <is>
-          <t>FAIL</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>Assertion failure on step 15</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="n">
-        <v>0.23</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>TC_ERR_005</t>
-        </is>
-      </c>
-      <c r="B7" s="2" t="inlineStr">
-        <is>
-          <t>Error Handling</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>Verify Automatic Reconnection &amp; Data Refetch Sync</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="E7" s="3" t="inlineStr">
-        <is>
-          <t>FAIL</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>Assertion failure on step 5</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="n">
-        <v>0.13</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>TC_UPLD_002</t>
-        </is>
-      </c>
-      <c r="B8" s="2" t="inlineStr">
-        <is>
-          <t>File Upload</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>Verify Android File Upload Feature Requirement #2 Compliance</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>P2</t>
-        </is>
-      </c>
-      <c r="E8" s="3" t="inlineStr">
-        <is>
-          <t>FAIL</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>Application crash on large file upload</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="n">
-        <v>0.1</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>TC_REGR_018</t>
-        </is>
-      </c>
-      <c r="B9" s="2" t="inlineStr">
-        <is>
-          <t>Regression Suite</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>Verify Prescription-Required Schedule H Drug Order Hold Enforcement</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>P3</t>
-        </is>
-      </c>
-      <c r="E9" s="3" t="inlineStr">
-        <is>
-          <t>FAIL</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>Assertion failure on step 18</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="n">
-        <v>0.26</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>TC_REGR_042</t>
-        </is>
-      </c>
-      <c r="B10" s="2" t="inlineStr">
-        <is>
-          <t>Regression Suite</t>
-        </is>
-      </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>Verify Automated Database Backup Sync Integrity Audit</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>P3</t>
-        </is>
-      </c>
-      <c r="E10" s="3" t="inlineStr">
-        <is>
-          <t>FAIL</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>Assertion failure on step 42</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="n">
-        <v>0.15</v>
       </c>
     </row>
   </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A2:E2"/>
+    <mergeCell ref="A1:E1"/>
+  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/Test Results/Excel/Failed_Test_Cases.xlsx
+++ b/Test Results/Excel/Failed_Test_Cases.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Failed Tests" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Failed Test Cases" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="4">
+  <fonts count="3">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -29,19 +29,11 @@
       <name val="Calibri"/>
       <b val="1"/>
       <color rgb="00FFFFFF"/>
-      <sz val="14"/>
+      <sz val="11"/>
     </font>
     <font>
-      <name val="Calibri"/>
-      <i val="1"/>
-      <color rgb="00475569"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
       <b val="1"/>
-      <color rgb="00FFFFFF"/>
-      <sz val="10"/>
+      <color rgb="009C0006"/>
     </font>
   </fonts>
   <fills count="4">
@@ -53,14 +45,14 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="001E3A8A"/>
-        <bgColor rgb="001E3A8A"/>
+        <fgColor rgb="001F4E78"/>
+        <bgColor rgb="001F4E78"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="000F172A"/>
-        <bgColor rgb="000F172A"/>
+        <fgColor rgb="00FFC7CE"/>
+        <bgColor rgb="00FFC7CE"/>
       </patternFill>
     </fill>
   </fills>
@@ -74,16 +66,16 @@
     </border>
     <border>
       <left style="thin">
-        <color rgb="00CBD5E1"/>
+        <color rgb="00D9D9D9"/>
       </left>
       <right style="thin">
-        <color rgb="00CBD5E1"/>
+        <color rgb="00D9D9D9"/>
       </right>
       <top style="thin">
-        <color rgb="00CBD5E1"/>
+        <color rgb="00D9D9D9"/>
       </top>
       <bottom style="thin">
-        <color rgb="00CBD5E1"/>
+        <color rgb="00D9D9D9"/>
       </bottom>
     </border>
   </borders>
@@ -95,11 +87,11 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -466,63 +458,371 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E4"/>
+  <dimension ref="A1:G10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="13" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="18" customWidth="1" min="5" max="5"/>
+    <col width="15" customWidth="1" min="1" max="1"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="71" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="42" customWidth="1" min="6" max="6"/>
+    <col width="22" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
-    <row r="1" ht="36" customHeight="1">
+    <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>❌ Failed Live Test Cases</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="18" customHeight="1">
+          <t>Test ID</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Module</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Test Name</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Priority</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Failure Reason</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Execution Time (s)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Live Deployment Target: https://Sanjeeva2431.github.io/medifind/ | Total Tests: 0</t>
-        </is>
-      </c>
-    </row>
-    <row r="3"/>
-    <row r="4" ht="24" customHeight="1">
-      <c r="A4" s="3" t="inlineStr">
-        <is>
-          <t>Test ID</t>
-        </is>
-      </c>
-      <c r="B4" s="3" t="inlineStr">
-        <is>
-          <t>Module</t>
-        </is>
-      </c>
-      <c r="C4" s="3" t="inlineStr">
-        <is>
-          <t>Test Name</t>
-        </is>
-      </c>
-      <c r="D4" s="3" t="inlineStr">
-        <is>
-          <t>Status</t>
+          <t>TC_AUTH_010</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>Authentication</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>Verify Logout Action Clears Native App Session Token</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>OTP validation mismatch</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="n">
+        <v>0.18</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>TC_FORM_008</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>Forms</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>Verify Forms Mobile Feature Step 8</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="E3" s="3" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>Validation message missing</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="n">
+        <v>0.16</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>TC_CRUD_022</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>CRUD Operations</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>Verify READ: List Nearby Active Pharmacy Partner Stores</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>Failure Reason</t>
-        </is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>Assertion failure on step 22</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="n">
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>TC_SRCH_014</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>Search</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>Verify Search Mobile Feature Step 14</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="E5" s="3" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>Assertion failure on step 14</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="n">
+        <v>0.22</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>TC_VAL_015</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>Input Validation</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>Verify File Size Exceeding 5MB Limit Rejection</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="E6" s="3" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>Assertion failure on step 15</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="n">
+        <v>0.23</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>TC_ERR_005</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>Error Handling</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>Verify Automatic Reconnection &amp; Data Refetch Sync</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="E7" s="3" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>Assertion failure on step 5</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="n">
+        <v>0.13</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>TC_UPLD_002</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>File Upload</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>Verify File Upload Mobile Feature Step 2</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="E8" s="3" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>Application crash on large file upload</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="n">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>TC_REGR_018</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>Regression Suite</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>Verify Prescription-Required Schedule H Drug Order Hold Enforcement</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>P3</t>
+        </is>
+      </c>
+      <c r="E9" s="3" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>Assertion failure on step 18</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="n">
+        <v>0.26</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>TC_REGR_042</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>Regression Suite</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>Verify Automated Database Backup Sync Integrity Audit</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>P3</t>
+        </is>
+      </c>
+      <c r="E10" s="3" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>Assertion failure on step 42</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="n">
+        <v>0.15</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="A2:E2"/>
-    <mergeCell ref="A1:E1"/>
-  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>